--- a/site/HR-to-Okta-Integration-Template-Version-History/headings.xlsx
+++ b/site/HR-to-Okta-Integration-Template-Version-History/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,28 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Template-Version-History/#h_01KH8AAX7AFMQZCC316FTNS9Z0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01M1K34JSQ2T63N7MCGSBJS5TM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-Integration-Template-Version-History/#h_01M1K34JSQ2T63N7MCGSBJS5TM</t>
         </is>
       </c>
     </row>
